--- a/clients/discoolver/deliverables/PLAN_LANZAMIENTO_2026-09-01.xlsx
+++ b/clients/discoolver/deliverables/PLAN_LANZAMIENTO_2026-09-01.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hitos'!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Riesgos'!$A$1:$D$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Promesas web'!$A$1:$E$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Estado por ciudad'!$A$2:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Estado por ciudad'!$A$2:$I$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Playbook ciudad'!$A$1:$E$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,11 +29,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -84,8 +83,20 @@
       <name val="Arial"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -137,8 +148,38 @@
         <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F2430"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7E6E6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -160,11 +201,16 @@
         <color rgb="00D8D4DA"/>
       </bottom>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -192,7 +238,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -204,7 +250,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -237,6 +283,49 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1363,10 +1452,10 @@
           <t>CEO</t>
         </is>
       </c>
-      <c r="F2" s="13" t="n">
+      <c r="F2" s="28" t="n">
         <v>46240</v>
       </c>
-      <c r="G2" s="13" t="n">
+      <c r="G2" s="28" t="n">
         <v>46240</v>
       </c>
       <c r="H2" s="11" t="inlineStr">
@@ -1416,10 +1505,10 @@
           <t>CEO</t>
         </is>
       </c>
-      <c r="F3" s="17" t="n">
+      <c r="F3" s="29" t="n">
         <v>46240</v>
       </c>
-      <c r="G3" s="17" t="n">
+      <c r="G3" s="29" t="n">
         <v>46240</v>
       </c>
       <c r="H3" s="15" t="inlineStr">
@@ -1469,10 +1558,10 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="F4" s="13" t="n">
+      <c r="F4" s="28" t="n">
         <v>46240</v>
       </c>
-      <c r="G4" s="13" t="n">
+      <c r="G4" s="28" t="n">
         <v>46241</v>
       </c>
       <c r="H4" s="11" t="inlineStr">
@@ -1522,10 +1611,10 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="F5" s="17" t="n">
+      <c r="F5" s="29" t="n">
         <v>46240</v>
       </c>
-      <c r="G5" s="17" t="n">
+      <c r="G5" s="29" t="n">
         <v>46241</v>
       </c>
       <c r="H5" s="15" t="inlineStr">
@@ -1575,10 +1664,10 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="28" t="n">
         <v>46240</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="G6" s="28" t="n">
         <v>46241</v>
       </c>
       <c r="H6" s="11" t="inlineStr">
@@ -1628,10 +1717,10 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="29" t="n">
         <v>46240</v>
       </c>
-      <c r="G7" s="17" t="n">
+      <c r="G7" s="29" t="n">
         <v>46246</v>
       </c>
       <c r="H7" s="15" t="inlineStr">
@@ -1681,10 +1770,10 @@
           <t>CEO</t>
         </is>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="28" t="n">
         <v>46240</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="28" t="n">
         <v>46247</v>
       </c>
       <c r="H8" s="11" t="inlineStr">
@@ -1734,10 +1823,10 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="29" t="n">
         <v>46240</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="G9" s="29" t="n">
         <v>46241</v>
       </c>
       <c r="H9" s="15" t="inlineStr">
@@ -1787,10 +1876,10 @@
           <t>Curador</t>
         </is>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="F10" s="28" t="n">
         <v>46241</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="G10" s="28" t="n">
         <v>46242</v>
       </c>
       <c r="H10" s="11" t="inlineStr">
@@ -1840,10 +1929,10 @@
           <t>Curador</t>
         </is>
       </c>
-      <c r="F11" s="17" t="n">
+      <c r="F11" s="29" t="n">
         <v>46241</v>
       </c>
-      <c r="G11" s="17" t="n">
+      <c r="G11" s="29" t="n">
         <v>46242</v>
       </c>
       <c r="H11" s="15" t="inlineStr">
@@ -1893,10 +1982,10 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="F12" s="28" t="n">
         <v>46241</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="G12" s="28" t="n">
         <v>46242</v>
       </c>
       <c r="H12" s="11" t="inlineStr">
@@ -1946,10 +2035,10 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="29" t="n">
         <v>46241</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="29" t="n">
         <v>46245</v>
       </c>
       <c r="H13" s="15" t="inlineStr">
@@ -1999,10 +2088,10 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="F14" s="28" t="n">
         <v>46241</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="G14" s="28" t="n">
         <v>46245</v>
       </c>
       <c r="H14" s="11" t="inlineStr">
@@ -2052,10 +2141,10 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="F15" s="17" t="n">
+      <c r="F15" s="29" t="n">
         <v>46241</v>
       </c>
-      <c r="G15" s="17" t="n">
+      <c r="G15" s="29" t="n">
         <v>46245</v>
       </c>
       <c r="H15" s="15" t="inlineStr">
@@ -2105,10 +2194,10 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="F16" s="28" t="n">
         <v>46241</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="G16" s="28" t="n">
         <v>46246</v>
       </c>
       <c r="H16" s="11" t="inlineStr">
@@ -2158,10 +2247,10 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="F17" s="17" t="n">
+      <c r="F17" s="29" t="n">
         <v>46241</v>
       </c>
-      <c r="G17" s="17" t="n">
+      <c r="G17" s="29" t="n">
         <v>46246</v>
       </c>
       <c r="H17" s="15" t="inlineStr">
@@ -2211,10 +2300,10 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="F18" s="13" t="n">
+      <c r="F18" s="28" t="n">
         <v>46241</v>
       </c>
-      <c r="G18" s="13" t="n">
+      <c r="G18" s="28" t="n">
         <v>46244</v>
       </c>
       <c r="H18" s="11" t="inlineStr">
@@ -2264,10 +2353,10 @@
           <t>CEO</t>
         </is>
       </c>
-      <c r="F19" s="17" t="n">
+      <c r="F19" s="29" t="n">
         <v>46241</v>
       </c>
-      <c r="G19" s="17" t="n">
+      <c r="G19" s="29" t="n">
         <v>46245</v>
       </c>
       <c r="H19" s="15" t="inlineStr">
@@ -2317,10 +2406,10 @@
           <t>Curador</t>
         </is>
       </c>
-      <c r="F20" s="13" t="n">
+      <c r="F20" s="28" t="n">
         <v>46244</v>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="G20" s="28" t="n">
         <v>46245</v>
       </c>
       <c r="H20" s="11" t="inlineStr">
@@ -2370,10 +2459,10 @@
           <t>Curador</t>
         </is>
       </c>
-      <c r="F21" s="17" t="n">
+      <c r="F21" s="29" t="n">
         <v>46244</v>
       </c>
-      <c r="G21" s="17" t="n">
+      <c r="G21" s="29" t="n">
         <v>46245</v>
       </c>
       <c r="H21" s="15" t="inlineStr">
@@ -2423,10 +2512,10 @@
           <t>CEO</t>
         </is>
       </c>
-      <c r="F22" s="13" t="n">
+      <c r="F22" s="28" t="n">
         <v>46244</v>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="G22" s="28" t="n">
         <v>46245</v>
       </c>
       <c r="H22" s="11" t="inlineStr">
@@ -2476,10 +2565,10 @@
           <t>CEO</t>
         </is>
       </c>
-      <c r="F23" s="17" t="n">
+      <c r="F23" s="29" t="n">
         <v>46244</v>
       </c>
-      <c r="G23" s="17" t="n">
+      <c r="G23" s="29" t="n">
         <v>46245</v>
       </c>
       <c r="H23" s="15" t="inlineStr">
@@ -2529,10 +2618,10 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="F24" s="13" t="n">
+      <c r="F24" s="28" t="n">
         <v>46244</v>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="G24" s="28" t="n">
         <v>46246</v>
       </c>
       <c r="H24" s="11" t="inlineStr">
@@ -2582,10 +2671,10 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="F25" s="17" t="n">
+      <c r="F25" s="29" t="n">
         <v>46244</v>
       </c>
-      <c r="G25" s="17" t="n">
+      <c r="G25" s="29" t="n">
         <v>46245</v>
       </c>
       <c r="H25" s="15" t="inlineStr">
@@ -2635,10 +2724,10 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="F26" s="13" t="n">
+      <c r="F26" s="28" t="n">
         <v>46244</v>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="G26" s="28" t="n">
         <v>46246</v>
       </c>
       <c r="H26" s="11" t="inlineStr">
@@ -2688,10 +2777,10 @@
           <t>Editor</t>
         </is>
       </c>
-      <c r="F27" s="17" t="n">
+      <c r="F27" s="29" t="n">
         <v>46245</v>
       </c>
-      <c r="G27" s="17" t="n">
+      <c r="G27" s="29" t="n">
         <v>46248</v>
       </c>
       <c r="H27" s="15" t="inlineStr">
@@ -2741,10 +2830,10 @@
           <t>Curador</t>
         </is>
       </c>
-      <c r="F28" s="13" t="n">
+      <c r="F28" s="28" t="n">
         <v>46245</v>
       </c>
-      <c r="G28" s="13" t="n">
+      <c r="G28" s="28" t="n">
         <v>46247</v>
       </c>
       <c r="H28" s="11" t="inlineStr">
@@ -2794,10 +2883,10 @@
           <t>CEO</t>
         </is>
       </c>
-      <c r="F29" s="17" t="n">
+      <c r="F29" s="29" t="n">
         <v>46244</v>
       </c>
-      <c r="G29" s="17" t="n">
+      <c r="G29" s="29" t="n">
         <v>46248</v>
       </c>
       <c r="H29" s="15" t="inlineStr">
@@ -2847,10 +2936,10 @@
           <t>CEO</t>
         </is>
       </c>
-      <c r="F30" s="13" t="n">
+      <c r="F30" s="28" t="n">
         <v>46245</v>
       </c>
-      <c r="G30" s="13" t="n">
+      <c r="G30" s="28" t="n">
         <v>46252</v>
       </c>
       <c r="H30" s="11" t="inlineStr">
@@ -2900,10 +2989,10 @@
           <t>Community</t>
         </is>
       </c>
-      <c r="F31" s="17" t="n">
+      <c r="F31" s="29" t="n">
         <v>46245</v>
       </c>
-      <c r="G31" s="17" t="n">
+      <c r="G31" s="29" t="n">
         <v>46248</v>
       </c>
       <c r="H31" s="15" t="inlineStr">
@@ -2953,10 +3042,10 @@
           <t>CEO</t>
         </is>
       </c>
-      <c r="F32" s="13" t="n">
+      <c r="F32" s="28" t="n">
         <v>46245</v>
       </c>
-      <c r="G32" s="13" t="n">
+      <c r="G32" s="28" t="n">
         <v>46245</v>
       </c>
       <c r="H32" s="11" t="inlineStr">
@@ -3006,10 +3095,10 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="F33" s="17" t="n">
+      <c r="F33" s="29" t="n">
         <v>46245</v>
       </c>
-      <c r="G33" s="17" t="n">
+      <c r="G33" s="29" t="n">
         <v>46253</v>
       </c>
       <c r="H33" s="15" t="inlineStr">
@@ -3059,10 +3148,10 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="F34" s="13" t="n">
+      <c r="F34" s="28" t="n">
         <v>46245</v>
       </c>
-      <c r="G34" s="13" t="n">
+      <c r="G34" s="28" t="n">
         <v>46248</v>
       </c>
       <c r="H34" s="11" t="inlineStr">
@@ -3112,10 +3201,10 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="F35" s="17" t="n">
+      <c r="F35" s="29" t="n">
         <v>46245</v>
       </c>
-      <c r="G35" s="17" t="n">
+      <c r="G35" s="29" t="n">
         <v>46248</v>
       </c>
       <c r="H35" s="15" t="inlineStr">
@@ -3165,10 +3254,10 @@
           <t>Curador</t>
         </is>
       </c>
-      <c r="F36" s="13" t="n">
+      <c r="F36" s="28" t="n">
         <v>46245</v>
       </c>
-      <c r="G36" s="13" t="n">
+      <c r="G36" s="28" t="n">
         <v>46252</v>
       </c>
       <c r="H36" s="11" t="inlineStr">
@@ -3218,10 +3307,10 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="F37" s="17" t="n">
+      <c r="F37" s="29" t="n">
         <v>46246</v>
       </c>
-      <c r="G37" s="17" t="n">
+      <c r="G37" s="29" t="n">
         <v>46248</v>
       </c>
       <c r="H37" s="15" t="inlineStr">
@@ -3271,10 +3360,10 @@
           <t>Curador</t>
         </is>
       </c>
-      <c r="F38" s="13" t="n">
+      <c r="F38" s="28" t="n">
         <v>46246</v>
       </c>
-      <c r="G38" s="13" t="n">
+      <c r="G38" s="28" t="n">
         <v>46248</v>
       </c>
       <c r="H38" s="11" t="inlineStr">
@@ -3324,10 +3413,10 @@
           <t>CEO</t>
         </is>
       </c>
-      <c r="F39" s="17" t="n">
+      <c r="F39" s="29" t="n">
         <v>46244</v>
       </c>
-      <c r="G39" s="17" t="n">
+      <c r="G39" s="29" t="n">
         <v>46255</v>
       </c>
       <c r="H39" s="15" t="inlineStr">
@@ -3377,10 +3466,10 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="F40" s="13" t="n">
+      <c r="F40" s="28" t="n">
         <v>46246</v>
       </c>
-      <c r="G40" s="13" t="n">
+      <c r="G40" s="28" t="n">
         <v>46252</v>
       </c>
       <c r="H40" s="11" t="inlineStr">
@@ -3430,10 +3519,10 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="F41" s="17" t="n">
+      <c r="F41" s="29" t="n">
         <v>46246</v>
       </c>
-      <c r="G41" s="17" t="n">
+      <c r="G41" s="29" t="n">
         <v>46251</v>
       </c>
       <c r="H41" s="15" t="inlineStr">
@@ -3483,10 +3572,10 @@
           <t>Curador</t>
         </is>
       </c>
-      <c r="F42" s="13" t="n">
+      <c r="F42" s="28" t="n">
         <v>46247</v>
       </c>
-      <c r="G42" s="13" t="n">
+      <c r="G42" s="28" t="n">
         <v>46251</v>
       </c>
       <c r="H42" s="11" t="inlineStr">
@@ -3536,10 +3625,10 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="F43" s="17" t="n">
+      <c r="F43" s="29" t="n">
         <v>46247</v>
       </c>
-      <c r="G43" s="17" t="n">
+      <c r="G43" s="29" t="n">
         <v>46253</v>
       </c>
       <c r="H43" s="15" t="inlineStr">
@@ -3589,10 +3678,10 @@
           <t>CEO</t>
         </is>
       </c>
-      <c r="F44" s="13" t="n">
+      <c r="F44" s="28" t="n">
         <v>46247</v>
       </c>
-      <c r="G44" s="13" t="n">
+      <c r="G44" s="28" t="n">
         <v>46252</v>
       </c>
       <c r="H44" s="11" t="inlineStr">
@@ -3642,10 +3731,10 @@
           <t>CEO</t>
         </is>
       </c>
-      <c r="F45" s="17" t="n">
+      <c r="F45" s="29" t="n">
         <v>46247</v>
       </c>
-      <c r="G45" s="17" t="n">
+      <c r="G45" s="29" t="n">
         <v>46254</v>
       </c>
       <c r="H45" s="15" t="inlineStr">
@@ -3695,10 +3784,10 @@
           <t>Curador</t>
         </is>
       </c>
-      <c r="F46" s="13" t="n">
+      <c r="F46" s="28" t="n">
         <v>46248</v>
       </c>
-      <c r="G46" s="13" t="n">
+      <c r="G46" s="28" t="n">
         <v>46252</v>
       </c>
       <c r="H46" s="11" t="inlineStr">
@@ -3748,10 +3837,10 @@
           <t>Curador</t>
         </is>
       </c>
-      <c r="F47" s="17" t="n">
+      <c r="F47" s="29" t="n">
         <v>46248</v>
       </c>
-      <c r="G47" s="17" t="n">
+      <c r="G47" s="29" t="n">
         <v>46253</v>
       </c>
       <c r="H47" s="15" t="inlineStr">
@@ -3801,10 +3890,10 @@
           <t>CEO</t>
         </is>
       </c>
-      <c r="F48" s="13" t="n">
+      <c r="F48" s="28" t="n">
         <v>46241</v>
       </c>
-      <c r="G48" s="13" t="n">
+      <c r="G48" s="28" t="n">
         <v>46248</v>
       </c>
       <c r="H48" s="11" t="inlineStr">
@@ -3854,10 +3943,10 @@
           <t>CEO</t>
         </is>
       </c>
-      <c r="F49" s="17" t="n">
+      <c r="F49" s="29" t="n">
         <v>46244</v>
       </c>
-      <c r="G49" s="17" t="n">
+      <c r="G49" s="29" t="n">
         <v>46246</v>
       </c>
       <c r="H49" s="15" t="inlineStr">
@@ -3907,10 +3996,10 @@
           <t>Diseño</t>
         </is>
       </c>
-      <c r="F50" s="13" t="n">
+      <c r="F50" s="28" t="n">
         <v>46246</v>
       </c>
-      <c r="G50" s="13" t="n">
+      <c r="G50" s="28" t="n">
         <v>46256</v>
       </c>
       <c r="H50" s="11" t="inlineStr">
@@ -3960,10 +4049,10 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="F51" s="17" t="n">
+      <c r="F51" s="29" t="n">
         <v>46251</v>
       </c>
-      <c r="G51" s="17" t="n">
+      <c r="G51" s="29" t="n">
         <v>46254</v>
       </c>
       <c r="H51" s="15" t="inlineStr">
@@ -4013,10 +4102,10 @@
           <t>Curador</t>
         </is>
       </c>
-      <c r="F52" s="13" t="n">
+      <c r="F52" s="28" t="n">
         <v>46251</v>
       </c>
-      <c r="G52" s="13" t="n">
+      <c r="G52" s="28" t="n">
         <v>46255</v>
       </c>
       <c r="H52" s="11" t="inlineStr">
@@ -4066,10 +4155,10 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="F53" s="17" t="n">
+      <c r="F53" s="29" t="n">
         <v>46251</v>
       </c>
-      <c r="G53" s="17" t="n">
+      <c r="G53" s="29" t="n">
         <v>46253</v>
       </c>
       <c r="H53" s="15" t="inlineStr">
@@ -4119,10 +4208,10 @@
           <t>Community</t>
         </is>
       </c>
-      <c r="F54" s="13" t="n">
+      <c r="F54" s="28" t="n">
         <v>46251</v>
       </c>
-      <c r="G54" s="13" t="n">
+      <c r="G54" s="28" t="n">
         <v>46254</v>
       </c>
       <c r="H54" s="11" t="inlineStr">
@@ -4172,10 +4261,10 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="F55" s="17" t="n">
+      <c r="F55" s="29" t="n">
         <v>46251</v>
       </c>
-      <c r="G55" s="17" t="n">
+      <c r="G55" s="29" t="n">
         <v>46254</v>
       </c>
       <c r="H55" s="15" t="inlineStr">
@@ -4225,10 +4314,10 @@
           <t>Community</t>
         </is>
       </c>
-      <c r="F56" s="13" t="n">
+      <c r="F56" s="28" t="n">
         <v>46251</v>
       </c>
-      <c r="G56" s="13" t="n">
+      <c r="G56" s="28" t="n">
         <v>46253</v>
       </c>
       <c r="H56" s="11" t="inlineStr">
@@ -4278,10 +4367,10 @@
           <t>CEO</t>
         </is>
       </c>
-      <c r="F57" s="17" t="n">
+      <c r="F57" s="29" t="n">
         <v>46251</v>
       </c>
-      <c r="G57" s="17" t="n">
+      <c r="G57" s="29" t="n">
         <v>46255</v>
       </c>
       <c r="H57" s="15" t="inlineStr">
@@ -4331,10 +4420,10 @@
           <t>Curador</t>
         </is>
       </c>
-      <c r="F58" s="13" t="n">
+      <c r="F58" s="28" t="n">
         <v>46252</v>
       </c>
-      <c r="G58" s="13" t="n">
+      <c r="G58" s="28" t="n">
         <v>46254</v>
       </c>
       <c r="H58" s="11" t="inlineStr">
@@ -4384,10 +4473,10 @@
           <t>Community</t>
         </is>
       </c>
-      <c r="F59" s="17" t="n">
+      <c r="F59" s="29" t="n">
         <v>46252</v>
       </c>
-      <c r="G59" s="17" t="n">
+      <c r="G59" s="29" t="n">
         <v>46254</v>
       </c>
       <c r="H59" s="15" t="inlineStr">
@@ -4437,10 +4526,10 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="F60" s="13" t="n">
+      <c r="F60" s="28" t="n">
         <v>46252</v>
       </c>
-      <c r="G60" s="13" t="n">
+      <c r="G60" s="28" t="n">
         <v>46254</v>
       </c>
       <c r="H60" s="11" t="inlineStr">
@@ -4490,10 +4579,10 @@
           <t>Editor</t>
         </is>
       </c>
-      <c r="F61" s="17" t="n">
+      <c r="F61" s="29" t="n">
         <v>46253</v>
       </c>
-      <c r="G61" s="17" t="n">
+      <c r="G61" s="29" t="n">
         <v>46258</v>
       </c>
       <c r="H61" s="15" t="inlineStr">
@@ -4543,10 +4632,10 @@
           <t>Curador</t>
         </is>
       </c>
-      <c r="F62" s="13" t="n">
+      <c r="F62" s="28" t="n">
         <v>46253</v>
       </c>
-      <c r="G62" s="13" t="n">
+      <c r="G62" s="28" t="n">
         <v>46256</v>
       </c>
       <c r="H62" s="11" t="inlineStr">
@@ -4596,10 +4685,10 @@
           <t>Community</t>
         </is>
       </c>
-      <c r="F63" s="17" t="n">
+      <c r="F63" s="29" t="n">
         <v>46253</v>
       </c>
-      <c r="G63" s="17" t="n">
+      <c r="G63" s="29" t="n">
         <v>46255</v>
       </c>
       <c r="H63" s="15" t="inlineStr">
@@ -4649,10 +4738,10 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="F64" s="13" t="n">
+      <c r="F64" s="28" t="n">
         <v>46253</v>
       </c>
-      <c r="G64" s="13" t="n">
+      <c r="G64" s="28" t="n">
         <v>46255</v>
       </c>
       <c r="H64" s="11" t="inlineStr">
@@ -4702,10 +4791,10 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="F65" s="17" t="n">
+      <c r="F65" s="29" t="n">
         <v>46253</v>
       </c>
-      <c r="G65" s="17" t="n">
+      <c r="G65" s="29" t="n">
         <v>46260</v>
       </c>
       <c r="H65" s="15" t="inlineStr">
@@ -4755,10 +4844,10 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="F66" s="13" t="n">
+      <c r="F66" s="28" t="n">
         <v>46253</v>
       </c>
-      <c r="G66" s="13" t="n">
+      <c r="G66" s="28" t="n">
         <v>46258</v>
       </c>
       <c r="H66" s="11" t="inlineStr">
@@ -4808,10 +4897,10 @@
           <t>Curador</t>
         </is>
       </c>
-      <c r="F67" s="17" t="n">
+      <c r="F67" s="29" t="n">
         <v>46254</v>
       </c>
-      <c r="G67" s="17" t="n">
+      <c r="G67" s="29" t="n">
         <v>46256</v>
       </c>
       <c r="H67" s="15" t="inlineStr">
@@ -4861,10 +4950,10 @@
           <t>Curador</t>
         </is>
       </c>
-      <c r="F68" s="13" t="n">
+      <c r="F68" s="28" t="n">
         <v>46254</v>
       </c>
-      <c r="G68" s="13" t="n">
+      <c r="G68" s="28" t="n">
         <v>46258</v>
       </c>
       <c r="H68" s="11" t="inlineStr">
@@ -4914,10 +5003,10 @@
           <t>Diseño</t>
         </is>
       </c>
-      <c r="F69" s="17" t="n">
+      <c r="F69" s="29" t="n">
         <v>46252</v>
       </c>
-      <c r="G69" s="17" t="n">
+      <c r="G69" s="29" t="n">
         <v>46258</v>
       </c>
       <c r="H69" s="15" t="inlineStr">
@@ -4967,10 +5056,10 @@
           <t>Curador</t>
         </is>
       </c>
-      <c r="F70" s="13" t="n">
+      <c r="F70" s="28" t="n">
         <v>46255</v>
       </c>
-      <c r="G70" s="13" t="n">
+      <c r="G70" s="28" t="n">
         <v>46258</v>
       </c>
       <c r="H70" s="11" t="inlineStr">
@@ -5020,10 +5109,10 @@
           <t>Editor</t>
         </is>
       </c>
-      <c r="F71" s="17" t="n">
+      <c r="F71" s="29" t="n">
         <v>46255</v>
       </c>
-      <c r="G71" s="17" t="n">
+      <c r="G71" s="29" t="n">
         <v>46259</v>
       </c>
       <c r="H71" s="15" t="inlineStr">
@@ -5073,10 +5162,10 @@
           <t>Diseño</t>
         </is>
       </c>
-      <c r="F72" s="13" t="n">
+      <c r="F72" s="28" t="n">
         <v>46255</v>
       </c>
-      <c r="G72" s="13" t="n">
+      <c r="G72" s="28" t="n">
         <v>46260</v>
       </c>
       <c r="H72" s="11" t="inlineStr">
@@ -5126,10 +5215,10 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="F73" s="17" t="n">
+      <c r="F73" s="29" t="n">
         <v>46255</v>
       </c>
-      <c r="G73" s="17" t="n">
+      <c r="G73" s="29" t="n">
         <v>46262</v>
       </c>
       <c r="H73" s="15" t="inlineStr">
@@ -5179,10 +5268,10 @@
           <t>Diseño</t>
         </is>
       </c>
-      <c r="F74" s="13" t="n">
+      <c r="F74" s="28" t="n">
         <v>46255</v>
       </c>
-      <c r="G74" s="13" t="n">
+      <c r="G74" s="28" t="n">
         <v>46262</v>
       </c>
       <c r="H74" s="11" t="inlineStr">
@@ -5232,10 +5321,10 @@
           <t>Editor</t>
         </is>
       </c>
-      <c r="F75" s="17" t="n">
+      <c r="F75" s="29" t="n">
         <v>46252</v>
       </c>
-      <c r="G75" s="17" t="n">
+      <c r="G75" s="29" t="n">
         <v>46258</v>
       </c>
       <c r="H75" s="15" t="inlineStr">
@@ -5285,10 +5374,10 @@
           <t>Editor</t>
         </is>
       </c>
-      <c r="F76" s="13" t="n">
+      <c r="F76" s="28" t="n">
         <v>46252</v>
       </c>
-      <c r="G76" s="13" t="n">
+      <c r="G76" s="28" t="n">
         <v>46255</v>
       </c>
       <c r="H76" s="11" t="inlineStr">
@@ -5338,10 +5427,10 @@
           <t>Curador</t>
         </is>
       </c>
-      <c r="F77" s="17" t="n">
+      <c r="F77" s="29" t="n">
         <v>46261</v>
       </c>
-      <c r="G77" s="17" t="n">
+      <c r="G77" s="29" t="n">
         <v>46266</v>
       </c>
       <c r="H77" s="15" t="inlineStr">
@@ -5391,10 +5480,10 @@
           <t>Editor</t>
         </is>
       </c>
-      <c r="F78" s="13" t="n">
+      <c r="F78" s="28" t="n">
         <v>46258</v>
       </c>
-      <c r="G78" s="13" t="n">
+      <c r="G78" s="28" t="n">
         <v>46259</v>
       </c>
       <c r="H78" s="11" t="inlineStr">
@@ -5444,10 +5533,10 @@
           <t>Editor</t>
         </is>
       </c>
-      <c r="F79" s="17" t="n">
+      <c r="F79" s="29" t="n">
         <v>46258</v>
       </c>
-      <c r="G79" s="17" t="n">
+      <c r="G79" s="29" t="n">
         <v>46260</v>
       </c>
       <c r="H79" s="15" t="inlineStr">
@@ -5497,10 +5586,10 @@
           <t>Curador</t>
         </is>
       </c>
-      <c r="F80" s="13" t="n">
+      <c r="F80" s="28" t="n">
         <v>46256</v>
       </c>
-      <c r="G80" s="13" t="n">
+      <c r="G80" s="28" t="n">
         <v>46259</v>
       </c>
       <c r="H80" s="11" t="inlineStr">
@@ -5550,10 +5639,10 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="F81" s="17" t="n">
+      <c r="F81" s="29" t="n">
         <v>46258</v>
       </c>
-      <c r="G81" s="17" t="n">
+      <c r="G81" s="29" t="n">
         <v>46259</v>
       </c>
       <c r="H81" s="15" t="inlineStr">
@@ -5603,10 +5692,10 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="F82" s="13" t="n">
+      <c r="F82" s="28" t="n">
         <v>46254</v>
       </c>
-      <c r="G82" s="13" t="n">
+      <c r="G82" s="28" t="n">
         <v>46260</v>
       </c>
       <c r="H82" s="11" t="inlineStr">
@@ -5656,10 +5745,10 @@
           <t>Editor</t>
         </is>
       </c>
-      <c r="F83" s="17" t="n">
+      <c r="F83" s="29" t="n">
         <v>46259</v>
       </c>
-      <c r="G83" s="17" t="n">
+      <c r="G83" s="29" t="n">
         <v>46261</v>
       </c>
       <c r="H83" s="15" t="inlineStr">
@@ -5709,10 +5798,10 @@
           <t>Editor</t>
         </is>
       </c>
-      <c r="F84" s="13" t="n">
+      <c r="F84" s="28" t="n">
         <v>46259</v>
       </c>
-      <c r="G84" s="13" t="n">
+      <c r="G84" s="28" t="n">
         <v>46260</v>
       </c>
       <c r="H84" s="11" t="inlineStr">
@@ -5762,10 +5851,10 @@
           <t>Editor</t>
         </is>
       </c>
-      <c r="F85" s="17" t="n">
+      <c r="F85" s="29" t="n">
         <v>46259</v>
       </c>
-      <c r="G85" s="17" t="n">
+      <c r="G85" s="29" t="n">
         <v>46261</v>
       </c>
       <c r="H85" s="15" t="inlineStr">
@@ -5815,10 +5904,10 @@
           <t>Editor</t>
         </is>
       </c>
-      <c r="F86" s="13" t="n">
+      <c r="F86" s="28" t="n">
         <v>46260</v>
       </c>
-      <c r="G86" s="13" t="n">
+      <c r="G86" s="28" t="n">
         <v>46262</v>
       </c>
       <c r="H86" s="11" t="inlineStr">
@@ -5868,10 +5957,10 @@
           <t>Editor</t>
         </is>
       </c>
-      <c r="F87" s="17" t="n">
+      <c r="F87" s="29" t="n">
         <v>46261</v>
       </c>
-      <c r="G87" s="17" t="n">
+      <c r="G87" s="29" t="n">
         <v>46262</v>
       </c>
       <c r="H87" s="15" t="inlineStr">
@@ -5921,10 +6010,10 @@
           <t>Editor</t>
         </is>
       </c>
-      <c r="F88" s="13" t="n">
+      <c r="F88" s="28" t="n">
         <v>46261</v>
       </c>
-      <c r="G88" s="13" t="n">
+      <c r="G88" s="28" t="n">
         <v>46262</v>
       </c>
       <c r="H88" s="11" t="inlineStr">
@@ -5974,10 +6063,10 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="F89" s="17" t="n">
+      <c r="F89" s="29" t="n">
         <v>46254</v>
       </c>
-      <c r="G89" s="17" t="n">
+      <c r="G89" s="29" t="n">
         <v>46261</v>
       </c>
       <c r="H89" s="15" t="inlineStr">
@@ -6027,10 +6116,10 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="F90" s="13" t="n">
+      <c r="F90" s="28" t="n">
         <v>46260</v>
       </c>
-      <c r="G90" s="13" t="n">
+      <c r="G90" s="28" t="n">
         <v>46261</v>
       </c>
       <c r="H90" s="11" t="inlineStr">
@@ -6080,10 +6169,10 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="F91" s="17" t="n">
+      <c r="F91" s="29" t="n">
         <v>46252</v>
       </c>
-      <c r="G91" s="17" t="n">
+      <c r="G91" s="29" t="n">
         <v>46255</v>
       </c>
       <c r="H91" s="15" t="inlineStr">
@@ -6133,10 +6222,10 @@
           <t>Diseño</t>
         </is>
       </c>
-      <c r="F92" s="13" t="n">
+      <c r="F92" s="28" t="n">
         <v>46258</v>
       </c>
-      <c r="G92" s="13" t="n">
+      <c r="G92" s="28" t="n">
         <v>46263</v>
       </c>
       <c r="H92" s="11" t="inlineStr">
@@ -6186,10 +6275,10 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="F93" s="17" t="n">
+      <c r="F93" s="29" t="n">
         <v>46258</v>
       </c>
-      <c r="G93" s="17" t="n">
+      <c r="G93" s="29" t="n">
         <v>46261</v>
       </c>
       <c r="H93" s="15" t="inlineStr">
@@ -6239,10 +6328,10 @@
           <t>Community</t>
         </is>
       </c>
-      <c r="F94" s="13" t="n">
+      <c r="F94" s="28" t="n">
         <v>46254</v>
       </c>
-      <c r="G94" s="13" t="n">
+      <c r="G94" s="28" t="n">
         <v>46263</v>
       </c>
       <c r="H94" s="11" t="inlineStr">
@@ -6292,10 +6381,10 @@
           <t>Community</t>
         </is>
       </c>
-      <c r="F95" s="17" t="n">
+      <c r="F95" s="29" t="n">
         <v>46259</v>
       </c>
-      <c r="G95" s="17" t="n">
+      <c r="G95" s="29" t="n">
         <v>46265</v>
       </c>
       <c r="H95" s="15" t="inlineStr">
@@ -6345,10 +6434,10 @@
           <t>Community</t>
         </is>
       </c>
-      <c r="F96" s="13" t="n">
+      <c r="F96" s="28" t="n">
         <v>46253</v>
       </c>
-      <c r="G96" s="13" t="n">
+      <c r="G96" s="28" t="n">
         <v>46261</v>
       </c>
       <c r="H96" s="11" t="inlineStr">
@@ -6398,10 +6487,10 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="F97" s="17" t="n">
+      <c r="F97" s="29" t="n">
         <v>46259</v>
       </c>
-      <c r="G97" s="17" t="n">
+      <c r="G97" s="29" t="n">
         <v>46265</v>
       </c>
       <c r="H97" s="15" t="inlineStr">
@@ -6451,10 +6540,10 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="F98" s="13" t="n">
+      <c r="F98" s="28" t="n">
         <v>46263</v>
       </c>
-      <c r="G98" s="13" t="n">
+      <c r="G98" s="28" t="n">
         <v>46265</v>
       </c>
       <c r="H98" s="11" t="inlineStr">
@@ -6504,10 +6593,10 @@
           <t>Editor</t>
         </is>
       </c>
-      <c r="F99" s="17" t="n">
+      <c r="F99" s="29" t="n">
         <v>46258</v>
       </c>
-      <c r="G99" s="17" t="n">
+      <c r="G99" s="29" t="n">
         <v>46265</v>
       </c>
       <c r="H99" s="15" t="inlineStr">
@@ -6557,10 +6646,10 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="F100" s="13" t="n">
+      <c r="F100" s="28" t="n">
         <v>46262</v>
       </c>
-      <c r="G100" s="13" t="n">
+      <c r="G100" s="28" t="n">
         <v>46265</v>
       </c>
       <c r="H100" s="11" t="inlineStr">
@@ -6610,10 +6699,10 @@
           <t>Community</t>
         </is>
       </c>
-      <c r="F101" s="17" t="n">
+      <c r="F101" s="29" t="n">
         <v>46260</v>
       </c>
-      <c r="G101" s="17" t="n">
+      <c r="G101" s="29" t="n">
         <v>46266</v>
       </c>
       <c r="H101" s="15" t="inlineStr">
@@ -6663,10 +6752,10 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="F102" s="13" t="n">
+      <c r="F102" s="28" t="n">
         <v>46260</v>
       </c>
-      <c r="G102" s="13" t="n">
+      <c r="G102" s="28" t="n">
         <v>46264</v>
       </c>
       <c r="H102" s="11" t="inlineStr">
@@ -6716,10 +6805,10 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="F103" s="17" t="n">
+      <c r="F103" s="29" t="n">
         <v>46253</v>
       </c>
-      <c r="G103" s="17" t="n">
+      <c r="G103" s="29" t="n">
         <v>46261</v>
       </c>
       <c r="H103" s="15" t="inlineStr">
@@ -6769,10 +6858,10 @@
           <t>Curador</t>
         </is>
       </c>
-      <c r="F104" s="13" t="n">
+      <c r="F104" s="28" t="n">
         <v>46247</v>
       </c>
-      <c r="G104" s="13" t="n">
+      <c r="G104" s="28" t="n">
         <v>46254</v>
       </c>
       <c r="H104" s="11" t="inlineStr">
@@ -6822,10 +6911,10 @@
           <t>CEO</t>
         </is>
       </c>
-      <c r="F105" s="17" t="n">
+      <c r="F105" s="29" t="n">
         <v>46258</v>
       </c>
-      <c r="G105" s="17" t="n">
+      <c r="G105" s="29" t="n">
         <v>46266</v>
       </c>
       <c r="H105" s="15" t="inlineStr">
@@ -6875,10 +6964,10 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="F106" s="13" t="n">
+      <c r="F106" s="28" t="n">
         <v>46258</v>
       </c>
-      <c r="G106" s="13" t="n">
+      <c r="G106" s="28" t="n">
         <v>46266</v>
       </c>
       <c r="H106" s="11" t="inlineStr">
@@ -6928,10 +7017,10 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="F107" s="17" t="n">
+      <c r="F107" s="29" t="n">
         <v>46260</v>
       </c>
-      <c r="G107" s="17" t="n">
+      <c r="G107" s="29" t="n">
         <v>46265</v>
       </c>
       <c r="H107" s="15" t="inlineStr">
@@ -6981,10 +7070,10 @@
           <t>CEO</t>
         </is>
       </c>
-      <c r="F108" s="13" t="n">
+      <c r="F108" s="28" t="n">
         <v>46261</v>
       </c>
-      <c r="G108" s="13" t="n">
+      <c r="G108" s="28" t="n">
         <v>46262</v>
       </c>
       <c r="H108" s="11" t="inlineStr">
@@ -7034,10 +7123,10 @@
           <t>Editor</t>
         </is>
       </c>
-      <c r="F109" s="17" t="n">
+      <c r="F109" s="29" t="n">
         <v>46262</v>
       </c>
-      <c r="G109" s="17" t="n">
+      <c r="G109" s="29" t="n">
         <v>46265</v>
       </c>
       <c r="H109" s="15" t="inlineStr">
@@ -7087,10 +7176,10 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="F110" s="13" t="n">
+      <c r="F110" s="28" t="n">
         <v>46259</v>
       </c>
-      <c r="G110" s="13" t="n">
+      <c r="G110" s="28" t="n">
         <v>46262</v>
       </c>
       <c r="H110" s="11" t="inlineStr">
@@ -7140,10 +7229,10 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="F111" s="17" t="n">
+      <c r="F111" s="29" t="n">
         <v>46265</v>
       </c>
-      <c r="G111" s="17" t="n">
+      <c r="G111" s="29" t="n">
         <v>46265</v>
       </c>
       <c r="H111" s="15" t="inlineStr">
@@ -7193,10 +7282,10 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="F112" s="13" t="n">
+      <c r="F112" s="28" t="n">
         <v>46265</v>
       </c>
-      <c r="G112" s="13" t="n">
+      <c r="G112" s="28" t="n">
         <v>46265</v>
       </c>
       <c r="H112" s="11" t="inlineStr">
@@ -7246,10 +7335,10 @@
           <t>Dev</t>
         </is>
       </c>
-      <c r="F113" s="17" t="n">
+      <c r="F113" s="29" t="n">
         <v>46266</v>
       </c>
-      <c r="G113" s="17" t="n">
+      <c r="G113" s="29" t="n">
         <v>46266</v>
       </c>
       <c r="H113" s="15" t="inlineStr">
@@ -7299,10 +7388,10 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="F114" s="13" t="n">
+      <c r="F114" s="28" t="n">
         <v>46266</v>
       </c>
-      <c r="G114" s="13" t="n">
+      <c r="G114" s="28" t="n">
         <v>46266</v>
       </c>
       <c r="H114" s="11" t="inlineStr">
@@ -7352,10 +7441,10 @@
           <t>CEO</t>
         </is>
       </c>
-      <c r="F115" s="17" t="n">
+      <c r="F115" s="29" t="n">
         <v>46244</v>
       </c>
-      <c r="G115" s="17" t="n">
+      <c r="G115" s="29" t="n">
         <v>46252</v>
       </c>
       <c r="H115" s="15" t="inlineStr">
@@ -7405,10 +7494,10 @@
           <t>CEO</t>
         </is>
       </c>
-      <c r="F116" s="13" t="n">
+      <c r="F116" s="28" t="n">
         <v>46240</v>
       </c>
-      <c r="G116" s="13" t="n">
+      <c r="G116" s="28" t="n">
         <v>46247</v>
       </c>
       <c r="H116" s="11" t="inlineStr">
@@ -7470,7 +7559,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="n">
+      <c r="A2" s="28" t="n">
         <v>46241</v>
       </c>
       <c r="B2" s="20" t="inlineStr">
@@ -7485,7 +7574,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="n">
+      <c r="A3" s="29" t="n">
         <v>46244</v>
       </c>
       <c r="B3" s="21" t="inlineStr">
@@ -7500,7 +7589,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="n">
+      <c r="A4" s="28" t="n">
         <v>46246</v>
       </c>
       <c r="B4" s="20" t="inlineStr">
@@ -7515,7 +7604,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="n">
+      <c r="A5" s="29" t="n">
         <v>46248</v>
       </c>
       <c r="B5" s="21" t="inlineStr">
@@ -7530,7 +7619,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="n">
+      <c r="A6" s="28" t="n">
         <v>46254</v>
       </c>
       <c r="B6" s="20" t="inlineStr">
@@ -7545,7 +7634,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="n">
+      <c r="A7" s="29" t="n">
         <v>46258</v>
       </c>
       <c r="B7" s="21" t="inlineStr">
@@ -7560,7 +7649,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="n">
+      <c r="A8" s="28" t="n">
         <v>46261</v>
       </c>
       <c r="B8" s="20" t="inlineStr">
@@ -7575,7 +7664,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="n">
+      <c r="A9" s="29" t="n">
         <v>46262</v>
       </c>
       <c r="B9" s="21" t="inlineStr">
@@ -7590,7 +7679,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="n">
+      <c r="A10" s="28" t="n">
         <v>46265</v>
       </c>
       <c r="B10" s="20" t="inlineStr">
@@ -7605,7 +7694,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="n">
+      <c r="A11" s="29" t="n">
         <v>46266</v>
       </c>
       <c r="B11" s="21" t="inlineStr">
@@ -10243,405 +10332,522 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="78" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>⚠ PENDIENTE DE ACTUALIZAR con el CSV de la BBDD de producción — los datos de abajo salen del dev.db local del editor de guías, no de la plataforma real.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>Ciudad / activo</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>Evidencia</t>
-        </is>
-      </c>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>Qué falta para abrir el 1-sept</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="30" t="inlineStr">
+        <is>
+          <t>Fuente: export de la BBDD de producción (Diego, 6-ago-2026) — _snapshot/bbdd/produccion_recomendaciones_2026-08-06.csv · 7.253 fichas, 6.861 vivas. Criterio: STATE=4 = recomendado (el primer STATE manda, la traducción se ignora). "Tarjeta lista" = viva + STATE=4 + foto principal + categoría.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="31" t="inlineStr">
+        <is>
+          <t>Ciudad</t>
+        </is>
+      </c>
+      <c r="B2" s="31" t="inlineStr">
+        <is>
+          <t>Fichas vivas</t>
+        </is>
+      </c>
+      <c r="C2" s="31" t="inlineStr">
+        <is>
+          <t>Recomendadas
+(STATE=4)</t>
+        </is>
+      </c>
+      <c r="D2" s="31" t="inlineStr">
+        <is>
+          <t>Con foto
+principal</t>
+        </is>
+      </c>
+      <c r="E2" s="31" t="inlineStr">
+        <is>
+          <t>TARJETAS
+LISTAS</t>
+        </is>
+      </c>
+      <c r="F2" s="31" t="inlineStr">
+        <is>
+          <t>Cola de revisión
+(STATE=3)</t>
+        </is>
+      </c>
+      <c r="G2" s="31" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
+      <c r="H2" s="31" t="inlineStr">
         <is>
           <t>Riesgo</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="I2" s="31" t="inlineStr">
+        <is>
+          <t>Qué significa y qué falta</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="118" customHeight="1">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Madrid</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>dev.db tabla `guides` (id 46cdc476…, tipo `influencer`, colección `foodie-selection`, director "Cenando con Pablo", status **draft**, creada 2026-08-05) · dev.db tabla `items`: **0 filas** para esa guía · curator.db tabla `city`: fila `madrid` sembrada con target_places=1000 · curator.db tabla `place`: **0 filas** · web/lib/content/home.ts línea 46-48 "Madrid según Cenando con Pablo · Desde 14€ · Próximamente"</t>
-        </is>
-      </c>
-      <c r="C3" s="16" t="inlineStr">
-        <is>
-          <t>Todo el contenido. La guía existe como carcasa vacía: cero fichas. Hace falta (1) ANTHROPIC_API_KEY en el .env del curador, (2) el primer harvest real de Apify que nunca se ha ejecutado, (3) sembrar el roster (discover → probe de ~900 cuentas → aprobar 25-30 a mano), (4) enrich con Maps + dependence + copy, (5) 5-10 h de desk, (6) contrato firmado con Cenando con Pablo y sesión de edición con él, (7) fotografía con derechos de impresión si sale en papel, (8) checkout de cobro (Gumroad/Lemon Squeezy sigue en ⏳ en ESTRATEGIA F0)</t>
-        </is>
-      </c>
-      <c r="D3" s="18" t="inlineStr">
-        <is>
-          <t>parcial</t>
-        </is>
-      </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="B3" s="33" t="n">
+        <v>5680</v>
+      </c>
+      <c r="C3" s="33" t="n">
+        <v>975</v>
+      </c>
+      <c r="D3" s="33" t="n">
+        <v>859</v>
+      </c>
+      <c r="E3" s="34" t="n">
+        <v>858</v>
+      </c>
+      <c r="F3" s="33" t="n">
+        <v>3775</v>
+      </c>
+      <c r="G3" s="35" t="inlineStr">
+        <is>
+          <t>ola 1</t>
+        </is>
+      </c>
+      <c r="H3" s="35" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="I3" s="36" t="inlineStr">
+        <is>
+          <t>Nada de contenido: 858 tarjetas listas, 14× el mínimo de una guía. El trabajo es EDITORIAL, no de recolección: elegir 60-80, ordenarlas por barrio y vibra, y reescribir el copy con voz de guía. Sigue faltando fotografía con derechos de impresión si hay papel, el contrato con Cenando con Pablo y el checkout. 20 de las 975 recomendadas son fichas de IA: revisarlas a mano antes de que entren.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="118" customHeight="1">
+      <c r="A4" s="32" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="n">
+        <v>237</v>
+      </c>
+      <c r="C4" s="33" t="n">
+        <v>196</v>
+      </c>
+      <c r="D4" s="33" t="n">
+        <v>182</v>
+      </c>
+      <c r="E4" s="34" t="n">
+        <v>182</v>
+      </c>
+      <c r="F4" s="33" t="n">
+        <v>37</v>
+      </c>
+      <c r="G4" s="35" t="inlineStr">
+        <is>
+          <t>ola 1</t>
+        </is>
+      </c>
+      <c r="H4" s="35" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="I4" s="36" t="inlineStr">
+        <is>
+          <t>182 tarjetas listas, todas curadas por personas (cero IA). Da para guía sin recolectar nada más. Falta creador que la firme — hoy no hay ninguno asignado a Barcelona.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="118" customHeight="1">
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>Ronda</t>
+        </is>
+      </c>
+      <c r="B5" s="33" t="n">
+        <v>247</v>
+      </c>
+      <c r="C5" s="33" t="n">
+        <v>188</v>
+      </c>
+      <c r="D5" s="33" t="n">
+        <v>166</v>
+      </c>
+      <c r="E5" s="34" t="n">
+        <v>165</v>
+      </c>
+      <c r="F5" s="33" t="n">
+        <v>38</v>
+      </c>
+      <c r="G5" s="35" t="inlineStr">
+        <is>
+          <t>ola 1</t>
+        </is>
+      </c>
+      <c r="H5" s="37" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="I5" s="36" t="inlineStr">
+        <is>
+          <t>165 listas y es el destino donde discoolver ya está desplegado (tótems, POS). Guía + caso 360 en la misma plaza. Ojo: es un destino pequeño, el mercado de una guía de pago es limitado; encaja mejor como pieza de venta B2B que como producto B2C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="118" customHeight="1">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B6" s="33" t="n">
+        <v>213</v>
+      </c>
+      <c r="C6" s="33" t="n">
+        <v>119</v>
+      </c>
+      <c r="D6" s="33" t="n">
+        <v>107</v>
+      </c>
+      <c r="E6" s="34" t="n">
+        <v>107</v>
+      </c>
+      <c r="F6" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="G6" s="37" t="inlineStr">
+        <is>
+          <t>ola 2</t>
+        </is>
+      </c>
+      <c r="H6" s="37" t="inlineStr">
+        <is>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="I6" s="36" t="inlineStr">
+        <is>
+          <t>107 listas: suficiente para una guía ajustada. 85 fichas en STATE=1 sin revisar que podrían subir el número. Sin creador asignado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="118" customHeight="1">
+      <c r="A7" s="32" t="inlineStr">
+        <is>
+          <t>Aranjuez</t>
+        </is>
+      </c>
+      <c r="B7" s="33" t="n">
+        <v>109</v>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>64</v>
+      </c>
+      <c r="D7" s="33" t="n">
+        <v>64</v>
+      </c>
+      <c r="E7" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="F7" s="33" t="n">
+        <v>42</v>
+      </c>
+      <c r="G7" s="37" t="inlineStr">
+        <is>
+          <t>ola 2</t>
+        </is>
+      </c>
+      <c r="H7" s="38" t="inlineStr">
         <is>
           <t>alto</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="26" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>dev.db `guides` id f6e6b7cc… status **draft**, últ. mod. 2026-08-05 08:54 (+ una segunda guía Barcelona del 2026-07-31 con 0 items) · `items`: 48 filas → **37 nombres únicos**; fichas de sitio (recomendado+persona_recom) 38 filas → **27 sitios distintos**; 4 eventos, 3 influencers, 3 timeline · exports/: 27 PDFs `barcelona-26_*`, el último 8,6 MB · verify_cascade.py línea 4: "96 fichas para 37 sitios distintos, 59 duplicados, MACBA seis veces"</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>Es la única ciudad con contenido real, pero no es publicable: **2 fotos de stock de Unsplash repetidas en 45 fichas** (16+16+7+6 usos) y 3 fichas sin foto → cero fotografía propia o licenciada; **0 fichas con `discoolver_url`** → no se puede imprimir un solo QR, que es el puente papel↔plataforma; **0 fichas con lat/lng** → los mapas ilustrados no pueden geolocalizar. 27 sitios está por debajo del cap editorial mínimo de la propia estrategia (50-100 venues). Falta: reponer la fotografía entera, las URLs canónicas de negocio (bloqueadas por los 500 del CMS de Diego), coordenadas, y subir de 27 a ~50 sitios. La ciudad ni siquiera existe como fila en `city` del curador</t>
-        </is>
-      </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>parcial</t>
-        </is>
-      </c>
-      <c r="E4" s="22" t="inlineStr">
+      <c r="I7" s="36" t="inlineStr">
+        <is>
+          <t>Justo en el mínimo (64). Y es una escapada de día desde Madrid, no una ciudad de guía propia: encaja mejor como capítulo dentro de Madrid que como edición independiente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="118" customHeight="1">
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>Ibiza</t>
+        </is>
+      </c>
+      <c r="B8" s="33" t="n">
+        <v>79</v>
+      </c>
+      <c r="C8" s="33" t="n">
+        <v>51</v>
+      </c>
+      <c r="D8" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="E8" s="39" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" s="33" t="n">
+        <v>28</v>
+      </c>
+      <c r="G8" s="37" t="inlineStr">
+        <is>
+          <t>ola 2</t>
+        </is>
+      </c>
+      <c r="H8" s="38" t="inlineStr">
         <is>
           <t>alto</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="25" t="inlineStr">
-        <is>
-          <t>Málaga / Costa del Sol</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>brand-brain.json `case_studies[1]`: "Proyecto Costa del Sol Tourism Hub — Señalética QR en puntos clave del destino. Integración marketplace" · briefing/index.html: 9 menciones de Costa del Sol · snapshot de discoolver.com: 17 menciones de "malaga" · dev.db: **0 guías, 0 items** · curator.db `city`: **no existe la fila**. "Málaga" no aparece ni una vez en brand-brain.json</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>Distinguir dos cosas que hoy se mezclan: como **despliegue B2B de la plataforma** (señalética QR, marketplace) es real y está vivo; como **guía curada** está exactamente a cero, igual que Sevilla. Para abrir una guía el 1-sep haría falta empezar de la nada: crear la ciudad en el curador, sembrar barrios/hashtags/roster, harvest, curación y fotografía. Si lo que se "abre" es la plataforma, ya está abierta y hay que decirlo así en el copy</t>
-        </is>
-      </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t>parcial</t>
-        </is>
-      </c>
-      <c r="E5" s="22" t="inlineStr">
-        <is>
-          <t>alto</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="26" t="inlineStr">
-        <is>
-          <t>Ronda</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>brand-brain.json `case_studies[0]`: "Proyecto Ronda — 200+ negocios y propuestas locales integradas. Totems interactivos. Venta cruzada con hoteles" · briefing/index.html: 40 menciones, es el *anchor case* ("Antes: turistas concentrados en el Puente Nuevo", testimonio del Director de Turismo, Mesón El Candil) · snapshot discoolver.com: 266 menciones · briefing KPI: "Destinos activos 2 → 30d: 3 → 90d: 7" · dev.db: **0 guías, 0 items** · curator.db: **no existe la fila de ciudad**</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Es el destino más real que tiene la empresa — pero del **producto B2B SaaS**, no del producto guías. 200+ negocios integrados, tótems, cliente de pago, oficina de turismo operando. Nada de eso es una ficha curada ni ha entrado nunca en el dg-editor ni en el curador. Para "abrir Ronda" el 1-sep no hace falta nada si se refiere a la plataforma (ya está abierta desde hace tiempo); si se refiere a una guía, hace falta todo. Oportunidad real: los 200+ negocios de Ronda son el único catálogo propio existente y podrían importarse como fichas si Diego arregla los 500 del CMS y da la URL canónica por negocio</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>parcial</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="I8" s="36" t="inlineStr">
+        <is>
+          <t>50 listas, por debajo del mínimo de 60. Faltan 10-30 fichas y 28 en cola de revisión que las darían. Producto muy estacional: lanzar en septiembre es lanzar al final de temporada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="118" customHeight="1">
+      <c r="A9" s="32" t="inlineStr">
+        <is>
+          <t>Punta Cana</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="n">
+        <v>140</v>
+      </c>
+      <c r="C9" s="33" t="n">
+        <v>134</v>
+      </c>
+      <c r="D9" s="33" t="n">
+        <v>129</v>
+      </c>
+      <c r="E9" s="34" t="n">
+        <v>128</v>
+      </c>
+      <c r="F9" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="40" t="inlineStr">
+        <is>
+          <t>fuera de plan</t>
+        </is>
+      </c>
+      <c r="H9" s="37" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="25" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>app-landing/lib/content/home.ts línea 40 `ticker_5: "Sevilla · 412 plazas restantes"`, línea 200 testimonio "Andrés P. · Local · Sevilla", línea 229 FAQ "Empezamos con 12: …Sevilla…", línea 249 CTA con las 12 ciudades, HeroForm.tsx línea 9 en el selector `CITIES` · **cero apariciones** en dev.db, curator.db, brand-brain.json, briefing, ESTADO_2026-08-06, ESTRATEGIA_EDITORIAL, OPERATIVA_PRODUCTO y el snapshot de discoolver.com</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Todo, empezando por existir. No hay ni una ficha, ni una guía, ni una fila de ciudad en el curador. Lo único que existe es copy con prueba social inventada — la propia ESTRATEGIA_EDITORIAL §5.4 ya lo diagnosticó ("Prueba social inventada… handles ficticios, '7 de 10 plazas' → sustituir por real") y la landing de la app sigue sirviéndola. En 26 días no hay forma de producir contenido real aquí. Decisión: o se retira Sevilla del copy, o se reencuadra explícitamente como "esta edición aún no existe"</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>no existe</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="inlineStr">
-        <is>
-          <t>alto</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="26" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>app-landing/lib/content/home.ts línea 42 `ticker_7: "Valencia · 333 plazas restantes"`, FAQ de 12 ciudades y CTA · HeroForm.tsx `CITIES` · exports/pitch/pitch-prueba-auditoria-valencia.pdf (un pitch de **prueba de auditoría**, no un creador real) · **cero apariciones** en dev.db, curator.db, brand-brain.json y briefing</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Idéntico a Sevilla: cero contenido, cero ciudad sembrada, cero creador. La única aparición de Valencia en material de producción es un PDF de pitch generado como prueba de una auditoría. Retirar del copy o reencuadrar como waitlist honesta</t>
-        </is>
-      </c>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>no existe</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>alto</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="25" t="inlineStr">
-        <is>
-          <t>Bilbao</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>app-landing/lib/content/home.ts línea 44 `ticker_9: "Bilbao · 156 plazas restantes"`, línea 209 testimonio "Sofía T. · Periodista · Bilbao", FAQ de 12 ciudades y CTA · creators-landing: 6 menciones · web/: 1 mención · **cero apariciones** en dev.db, curator.db, brand-brain.json, briefing y el snapshot de discoolver.com</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Igual que Sevilla y Valencia: no existe nada más allá del copy y de un testimonio inventado. Retirar o reencuadrar</t>
-        </is>
-      </c>
-      <c r="D9" s="22" t="inlineStr">
-        <is>
-          <t>no existe</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="inlineStr">
-        <is>
-          <t>alto</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="26" t="inlineStr">
-        <is>
-          <t>Bangkok</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>dev.db `guides`: **dos** guías Bangkok 2026, una `world` y otra `influencer`, ambas con director "Travis Leon", ambas **draft**, ambas con **0 items** · curator.db `city`: fila `bangkok` sembrada, target_places=500, **0 places** · exports/pitch/pitch-travis-leon-bangkok.pdf (pitch generado, sin portada) · web/lib/content/home.ts: "Bangkok según Travis Leon · Próximamente"</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>Cero fichas. Dos guías duplicadas y vacías que además hay que consolidar en una (¿línea creator o línea mundo?). Falta contrato firmado con Travis Leon, el harvest nunca ejecutado, y toda la curación. A favor: la ciudad está sembrada en el curador y Carlos está físicamente en Bangkok, lo que resuelve el problema de fotografía propia con derechos de impresión — el único sitio donde eso es resoluble en 26 días</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>parcial</t>
-        </is>
-      </c>
-      <c r="E10" s="22" t="inlineStr">
-        <is>
-          <t>alto</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="25" t="inlineStr">
-        <is>
-          <t>Colecciones (las 12 temáticas)</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>OPERATIVA_PRODUCTO.md §Colecciones: "Hoy son 12 hardcodeadas en `editor/src/pages/GuideNew.jsx`… Decisión CEO: pasarlas a editables desde el propio editor (tabla + CRUD + selector alimentado por API). → **Feature pendiente de construir**" · dev.db `guides.collection`: solo se han usado **2 valores** en 5 guías (`estandar` ×4, `foodie-selection` ×1) · ESTADO §6.2: faltan `wellness` y `naturaleza` en CANONICAL_SECTIONS</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>Las 12 colecciones existen como lista fija en el código del editor, no como dato: no hay tabla, ni CRUD, ni API. 10 de las 12 no se han usado nunca. Además dos secciones de la taxonomía del curador (`wellness`, `naturaleza`) no están en `CANONICAL_SECTIONS` de `app/models/guide_v2.py` **y no tienen plantilla en `design/`** — sin plantilla la sección no imprime. Si el lanzamiento promete colecciones temáticas, hay que construir el CRUD y las dos plantillas que faltan</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>parcial</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="I9" s="36" t="inlineStr">
+        <is>
+          <t>128 listas y listas de verdad. No estaba en el plan del 1-sept y no hay creador ni mercado definido. Decisión de negocio: ¿el Caribe es mercado objetivo o es herencia del catálogo antiguo?</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="118" customHeight="1">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="n">
+        <v>80</v>
+      </c>
+      <c r="C10" s="33" t="n">
+        <v>75</v>
+      </c>
+      <c r="D10" s="33" t="n">
+        <v>75</v>
+      </c>
+      <c r="E10" s="34" t="n">
+        <v>75</v>
+      </c>
+      <c r="F10" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="40" t="inlineStr">
+        <is>
+          <t>fuera de plan</t>
+        </is>
+      </c>
+      <c r="H10" s="37" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>Curador (discoolver-curator)</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>curator.db consultada en solo lectura: `place` **0** · `candidate` **0** · `post` **0** · `mention` **0** · `harvest_run` **0** · `place_copy` **0** · `review_action` **0** · `event` **0** · `source` **0**. `city` = 3 filas (Madrid, "Madrid (prueba)", Bangkok) · .env: APIFY_TOKEN presente (46 chars, puesto hoy) pero **ANTHROPIC_API_KEY vacía (longitud 0)** · curator.log arranque de hoy 11:39: "ANTHROPIC_API_KEY no configurada — la extracción devolverá 503" · README §Estado: "F0 y F1 completos y verificados — 23/23 comprobaciones"</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>**El curador no puede producir ni una sola ficha hoy.** La extracción (el paso que convierte posts en candidatos) devuelve 503 por falta de ANTHROPIC_API_KEY. Nunca se ha ejecutado un `harvest_run`: las 46 verificaciones (F0/F1/F2/F3) corren sobre fixtures sintéticas, no sobre datos reales. Solo 3 ciudades sembradas de las 8 del plan — Barcelona, Málaga, Ronda, Sevilla, Valencia y Bilbao no existen ni como fila. Falta: la API key (5 minutos del CEO), el primer harvest real y el calibrado que siempre trae (entity resolution, geocodificación, percentiles por ciudad×categoría), y sembrar 5-6 ciudades a mano. El repo tampoco tiene remoto creado en GitHub</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>parcial</t>
-        </is>
-      </c>
-      <c r="E12" s="22" t="inlineStr">
-        <is>
-          <t>alto</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="25" t="inlineStr">
-        <is>
-          <t>Guías en PDF (el producto vendible)</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>exports/: 27 PDFs, **todos `barcelona-26_*`**, ninguno de Madrid ni Bangkok jamás · último export 2026-08-05 22:52, 8,6 MB · ESTADO §2 "Export a PDF: Funciona — 33 páginas" · ESTADO §6.5: "para una foto a sangre en A4 a 300 dpi hacen falta ~2500 px y hoy las fichas traen 800-1400" · ESTADO §7: "Hoy nada impide exportar una guía con fotos repetidas o fichas sin foto propia: la guía de ejemplo comparte 2 fotos entre 39 fichas" · `guide_snapshots`: 31</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>El **motor** funciona de verdad y está verificado (Playwright + PyMuPDF, 6 layouts, lector móvil sin conexión). Lo que no existe es un PDF **vendible**: la única guía exportada usa 2 fotos de stock de Unsplash, no tiene QRs (0 `discoolver_url`) y no tiene resolución para imprenta. Curar de RRSS no da derecho a imprimir; el papel exige licencia explícita. Falta además: cola de trabajo (un export tarda 2-3 min y bloquea), validación que impida exportar con fotos repetidas o sin foto, y reescalado de las fotos que cachea el lector (una guía de 40 fotos ocupa 50-80 MB en el móvil)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>parcial</t>
-        </is>
-      </c>
-      <c r="E13" s="22" t="inlineStr">
-        <is>
-          <t>alto</t>
+      <c r="I10" s="36" t="inlineStr">
+        <is>
+          <t>75 listas. Mismo caso que Punta Cana: contenido listo sin plan comercial detrás.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="118" customHeight="1">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="n">
+        <v>11</v>
+      </c>
+      <c r="C11" s="33" t="n">
+        <v>11</v>
+      </c>
+      <c r="D11" s="33" t="n">
+        <v>11</v>
+      </c>
+      <c r="E11" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="41" t="inlineStr">
+        <is>
+          <t>descartar</t>
+        </is>
+      </c>
+      <c r="H11" s="33" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I11" s="36" t="inlineStr">
+        <is>
+          <t>Solo 11 fichas. No es una ciudad del catálogo, es un residuo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="118" customHeight="1">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>Filipinas</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="n">
+        <v>65</v>
+      </c>
+      <c r="C12" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="E12" s="39" t="n">
+        <v>50</v>
+      </c>
+      <c r="F12" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="38" t="inlineStr">
+        <is>
+          <t>limpiar</t>
+        </is>
+      </c>
+      <c r="H12" s="33" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I12" s="36" t="inlineStr">
+        <is>
+          <t>NO ES UNA CIUDAD. Es un cajón de sastre con hoteles y bares internacionales (Burj Al Arab de Dubái, Ashford Castle en Irlanda, Marina Bay Sands de Singapur, bares de Londres y Roma). Las 50 fichas recomendadas hay que reasignarlas a su ciudad real o retirarlas: hoy ensucian cualquier recuento.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
-        <is>
-          <t>Comunidades de WhatsApp</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>Búsqueda exhaustiva en clients/discoolver/ (web, app-landing, creators-landing, brand-brain.json, briefing), dg-editor (*.md, dev.db) y curator (*.md, curator.db). Las **únicas** apariciones de "whatsapp" son botones de compartir dentro del HTML del snapshot de la web antigua y una mención en el briefing; **no hay tabla, ni contenido, ni copy, ni documento** que describa o prometa comunidades de WhatsApp por ciudad</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>Todo, o aclarar de dónde sale la promesa. No hay ninguna traza de este activo en ninguno de los tres repos ni en las cuatro webs: ni un enlace de invitación, ni un listado de grupos, ni un responsable, ni una mención en la estrategia editorial. Si forma parte del lanzamiento del 1-sep, hoy existe solo en la cabeza del CEO: hay que definir quién modera, con qué contenido diario y en qué ciudades — y 8 comunidades sin contenido que compartir mueren en dos semanas</t>
-        </is>
-      </c>
-      <c r="D14" s="22" t="inlineStr">
-        <is>
-          <t>no existe</t>
-        </is>
-      </c>
-      <c r="E14" s="22" t="inlineStr">
-        <is>
-          <t>alto</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="25" t="inlineStr">
-        <is>
-          <t>Creadores firmados</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>exports/pitch/: pitch-cenando-con-pablo-madrid (HTML+PDF), pitch-travis-leon-bangkok (HTML+PDF), pitch-prueba-auditoria-valencia (prueba) · exports/portadas/: **solo** portada-cenando-con-pablo-madrid.png · deliverables/ACUERDO_CREATOR.md: **plantilla con placeholders** `[NOMBRE / MARCA DEL CREATOR]`, `[CIUDAD]`, `[AÑO]` · ESTRATEGIA F0: "⏳ Contrato-tipo creator" y "⏳ Alta Gumroad/Lemon Squeezy" · dev.db `users`: 3 filas, el único con rol `influencer` tiene email `no-soy-un-email` (usuario de prueba) · `instagram_connections` y `user_instagram`: **0 filas**</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>**Cero creadores firmados.** Hay dos pilotos identificados (Cenando con Pablo → Madrid, Travis Leon → Bangkok) con pitch generado, pero el acuerdo es una plantilla sin rellenar y no consta ninguna firma. Además: el portal de influencers está EN PAUSA por decisión de producto (OPERATIVA §Guías de influencer: "No provisionar usuarios aún"), la ingesta de posts del creador nunca ha corrido (0 conexiones de Instagram, y la de Apify del dg-editor está condenada a retirarse), y falta la pasarela de cobro para pagarles el 50/50. Sin contrato firmado no hay licencia de contenido — y sin licencia no se puede publicar ni vender su guía</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>parcial</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="inlineStr">
-        <is>
-          <t>alto</t>
+      <c r="A14" s="42" t="inlineStr">
+        <is>
+          <t>LO QUE NO ESTÁ EN LA BBDD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Bangkok: CERO fichas. El plan del 1-sept la daba como una de las ocho plazas. Se construye desde nada — no hay atajo y no cabe en 26 días.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Sevilla, Valencia, Bilbao, Granada, San Sebastián, Córdoba: CERO fichas. Ninguna de las ciudades españolas "obvias" existe en el catálogo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Las "7 ciudades de España" del plan no existen: solo hay 5 españolas con contenido real (Madrid, Barcelona, Ronda, Málaga, Aranjuez) más Ibiza por debajo del mínimo. El objetivo hay que reescribirlo sobre lo que hay, no al revés.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="42" t="inlineStr">
+        <is>
+          <t>EL CUELLO DE BOTELLA REAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>La máquina de recolección SÍ funciona: 4.605 de las 6.861 fichas vivas (67%) las generó la IA. Corregido: lo que parecía "el curador nunca ha arrancado" era el dev.db local del editor. no producción.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Lo que NO funciona es la revisión: 3.935 fichas esperando en STATE=3. el 94% generadas por IA y solo el 6% con alguna foto. Recolectar es gratis; revisar y fotografiar es el trabajo caro. y es el que no se ha hecho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Traducción al plan: el 1 de septiembre no lo decide cuántas fichas hay, lo deciden las horas de edición humana y la fotografía con derechos. Madrid, Barcelona y Ronda ya tienen material de sobra; lo que falta es editor, fotógrafo y creador que firme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza rápida antes de publicar nada: 56 fichas recomendadas sin ninguna foto, 15 sin categoría, 2 con etiquetas HTML &lt;b&gt; en el nombre, 6 nombres duplicados y 4 fichas de prueba de Diego.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E2"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+  <autoFilter ref="A2:I12"/>
+  <mergeCells count="8">
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A16:I16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
